--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ69"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7525,10 +7525,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127760144</v>
+        <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99140</v>
+        <v>99259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7536,41 +7536,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skrållan, Hjd</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385827</v>
+        <v>385583</v>
       </c>
       <c r="R67" t="n">
-        <v>6973404</v>
+        <v>6972958</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7594,12 +7590,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7614,31 +7610,31 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Bergström, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127760144</t>
+          <t>https://artportalen.se/Sighting/136531944</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>72225318</v>
+        <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99038</v>
+        <v>99344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7646,41 +7642,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223597</v>
+        <v>219811</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stig längs med Ljungan, Ljungdalen, Hjd</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385828</v>
+        <v>385602</v>
       </c>
       <c r="R68" t="n">
-        <v>6973213</v>
+        <v>6972908</v>
       </c>
       <c r="S68" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7704,22 +7696,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7728,34 +7710,37 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Thomas Bergman</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Thomas Bergman</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72225318</t>
+          <t>https://artportalen.se/Sighting/136531629</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>104488273</v>
+        <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>80398</v>
+        <v>99344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7763,38 +7748,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229748</v>
+        <v>219811</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Älgen 6, Berg, Hjd</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385710</v>
+        <v>385628</v>
       </c>
       <c r="R69" t="n">
-        <v>6973330</v>
+        <v>6972861</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7818,12 +7802,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7838,16 +7822,880 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136531832</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136531858</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>385654</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6972828</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136531858</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136532177</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>385606</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6972897</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136532177</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136532190</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>385579</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6972977</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136532190</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136531502</v>
+      </c>
+      <c r="B73" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>385608</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6972896</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136531502</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136532154</v>
+      </c>
+      <c r="B74" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>385589</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6972939</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136532154</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127760144</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skrållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>385827</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6973404</v>
+      </c>
+      <c r="S75" t="n">
+        <v>50</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Bergström, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127760144</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>72225318</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stig längs med Ljungan, Ljungdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>385828</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6973213</v>
+      </c>
+      <c r="S76" t="n">
+        <v>100</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2018-06-20</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2018-06-20</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Thomas Bergman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Thomas Bergman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72225318</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>104488273</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Älgen 6, Berg, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>385710</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6973330</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104488273</t>
         </is>
@@ -7923,6 +8771,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -8145,7 +8145,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">

--- a/artfynd/A 48260-2022 artfynd.xlsx
+++ b/artfynd/A 48260-2022 artfynd.xlsx
@@ -7528,7 +7528,7 @@
         <v>136531944</v>
       </c>
       <c r="B67" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>136531629</v>
       </c>
       <c r="B68" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>136531832</v>
       </c>
       <c r="B69" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>136531858</v>
       </c>
       <c r="B70" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>136532177</v>
       </c>
       <c r="B71" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>136532190</v>
       </c>
       <c r="B72" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136531502</v>
       </c>
       <c r="B73" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136532154</v>
       </c>
       <c r="B74" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
